--- a/MAJSushiConfig/ig/FRAuthorLMCDAFHIR.xlsx
+++ b/MAJSushiConfig/ig/FRAuthorLMCDAFHIR.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/metier/document-core/ConceptMap/FRAuthorLMCDAFHIR</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/ConceptMap/FRAuthorLMCDAFHIR</t>
   </si>
   <si>
     <t>Version</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:25:17+00:00</t>
+    <t>2026-09-07T11:26:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -108,7 +108,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMHeaderDocument</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMHeaderDocument|0.1.0</t>
   </si>
   <si>
     <t/>

--- a/MAJSushiConfig/ig/FRAuthorLMCDAFHIR.xlsx
+++ b/MAJSushiConfig/ig/FRAuthorLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="40">
   <si>
     <t>Property</t>
   </si>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T11:26:50+00:00</t>
+    <t>2026-09-07T11:40:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -455,32 +455,6 @@
         <v>37</v>
       </c>
       <c r="E4" s="2"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D5" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D6" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="E6" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -489,7 +463,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -539,45 +513,6 @@
       </c>
       <c r="E3" s="2"/>
     </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D4" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D5" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D6" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="E6" s="2"/>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
